--- a/Excel/Abstract.xlsx
+++ b/Excel/Abstract.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annar\OneDrive\Desktop\Progetto_Vegna_DH\Sito_web\Dati\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umbov\Desktop\Sito_web\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B99DA1-4AFF-46A4-9477-8F9A0B0ADCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705E94CE-9451-4B5B-BFBB-1E37CD1469EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="721" xr2:uid="{84604206-B8D9-4EFC-82BD-355A00B61ABD}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="721" xr2:uid="{84604206-B8D9-4EFC-82BD-355A00B61ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="290">
   <si>
     <t>argomento</t>
   </si>
@@ -906,6 +906,9 @@
   </si>
   <si>
     <t>http://vocab.getty.edu/page/tgn/1000070</t>
+  </si>
+  <si>
+    <t>https://vegnachristian14.github.io/Prima-Repubblica-prime-elezioni/Item_1.html</t>
   </si>
 </sst>
 </file>
@@ -1303,16 +1306,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86800FC7-B318-4178-AEED-A57807F7D6C7}">
   <dimension ref="A1:E144"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="1" max="1" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1329,7 +1332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1346,7 +1349,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1363,7 +1366,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1380,7 +1383,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1397,7 +1400,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>107</v>
       </c>
@@ -1414,7 +1417,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1431,7 +1434,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1448,7 +1451,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1465,7 +1468,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1482,7 +1485,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1499,7 +1502,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1516,7 +1519,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1533,7 +1536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1550,7 +1553,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1567,7 +1570,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1584,7 +1587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1601,7 +1604,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1618,7 +1621,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1652,7 +1655,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1669,7 +1672,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1686,7 +1689,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1703,7 +1706,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -1720,7 +1723,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -1737,7 +1740,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>138</v>
       </c>
@@ -1754,7 +1757,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1771,7 +1774,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -1788,7 +1791,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -1805,7 +1808,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -1822,7 +1825,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1839,7 +1842,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -1856,7 +1859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -1873,7 +1876,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1890,7 +1893,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>121</v>
       </c>
@@ -1907,7 +1910,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -1924,7 +1927,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -1941,7 +1944,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -1958,7 +1961,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -1975,7 +1978,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>77</v>
       </c>
@@ -1992,7 +1995,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -2009,7 +2012,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -2026,7 +2029,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>83</v>
       </c>
@@ -2043,7 +2046,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>84</v>
       </c>
@@ -2060,7 +2063,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -2077,7 +2080,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -2094,7 +2097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>92</v>
       </c>
@@ -2111,7 +2114,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>93</v>
       </c>
@@ -2128,7 +2131,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -2145,7 +2148,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>95</v>
       </c>
@@ -2162,7 +2165,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>100</v>
       </c>
@@ -2179,7 +2182,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>102</v>
       </c>
@@ -2196,7 +2199,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>103</v>
       </c>
@@ -2213,7 +2216,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -2230,7 +2233,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>105</v>
       </c>
@@ -2247,7 +2250,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>106</v>
       </c>
@@ -2264,7 +2267,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>113</v>
       </c>
@@ -2281,7 +2284,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -2298,7 +2301,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -2315,7 +2318,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>117</v>
       </c>
@@ -2332,7 +2335,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>123</v>
       </c>
@@ -2349,7 +2352,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>125</v>
       </c>
@@ -2366,7 +2369,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>122</v>
       </c>
@@ -2383,7 +2386,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -2400,7 +2403,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>127</v>
       </c>
@@ -2417,7 +2420,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>128</v>
       </c>
@@ -2434,7 +2437,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>129</v>
       </c>
@@ -2451,7 +2454,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>134</v>
       </c>
@@ -2468,7 +2471,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>136</v>
       </c>
@@ -2485,7 +2488,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>139</v>
       </c>
@@ -2502,7 +2505,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>140</v>
       </c>
@@ -2519,7 +2522,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>142</v>
       </c>
@@ -2536,7 +2539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>146</v>
       </c>
@@ -2553,7 +2556,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>148</v>
       </c>
@@ -2570,7 +2573,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>149</v>
       </c>
@@ -2587,7 +2590,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>150</v>
       </c>
@@ -2604,7 +2607,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -2621,7 +2624,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>154</v>
       </c>
@@ -2638,7 +2641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -2655,7 +2658,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>158</v>
       </c>
@@ -2672,7 +2675,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>164</v>
       </c>
@@ -2689,7 +2692,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>162</v>
       </c>
@@ -2706,7 +2709,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>165</v>
       </c>
@@ -2723,7 +2726,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>167</v>
       </c>
@@ -2740,7 +2743,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>170</v>
       </c>
@@ -2757,7 +2760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>171</v>
       </c>
@@ -2774,7 +2777,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>173</v>
       </c>
@@ -2788,10 +2791,10 @@
         <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>175</v>
       </c>
@@ -2805,10 +2808,10 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>176</v>
       </c>
@@ -2822,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>177</v>
       </c>
@@ -2839,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>178</v>
       </c>
@@ -2859,7 +2862,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>179</v>
       </c>
@@ -2873,10 +2876,10 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>180</v>
       </c>
@@ -2890,10 +2893,10 @@
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>181</v>
       </c>
@@ -2907,10 +2910,10 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>182</v>
       </c>
@@ -2924,10 +2927,10 @@
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>191</v>
       </c>
@@ -2944,7 +2947,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>192</v>
       </c>
@@ -2961,7 +2964,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>193</v>
       </c>
@@ -2978,7 +2981,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>203</v>
       </c>
@@ -2995,7 +2998,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>204</v>
       </c>
@@ -3012,7 +3015,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>205</v>
       </c>
@@ -3029,7 +3032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>194</v>
       </c>
@@ -3046,7 +3049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>195</v>
       </c>
@@ -3063,7 +3066,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>197</v>
       </c>
@@ -3080,7 +3083,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>198</v>
       </c>
@@ -3097,7 +3100,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>211</v>
       </c>
@@ -3114,7 +3117,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>213</v>
       </c>
@@ -3131,7 +3134,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>215</v>
       </c>
@@ -3148,7 +3151,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>217</v>
       </c>
@@ -3165,7 +3168,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>220</v>
       </c>
@@ -3182,7 +3185,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>221</v>
       </c>
@@ -3199,7 +3202,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>224</v>
       </c>
@@ -3216,7 +3219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>225</v>
       </c>
@@ -3233,7 +3236,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>226</v>
       </c>
@@ -3250,7 +3253,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>229</v>
       </c>
@@ -3267,7 +3270,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>231</v>
       </c>
@@ -3284,7 +3287,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>233</v>
       </c>
@@ -3301,7 +3304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>235</v>
       </c>
@@ -3318,7 +3321,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>237</v>
       </c>
@@ -3335,7 +3338,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>239</v>
       </c>
@@ -3352,7 +3355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>241</v>
       </c>
@@ -3369,7 +3372,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>243</v>
       </c>
@@ -3386,7 +3389,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>245</v>
       </c>
@@ -3403,7 +3406,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>247</v>
       </c>
@@ -3420,7 +3423,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -3437,7 +3440,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>251</v>
       </c>
@@ -3454,7 +3457,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -3471,7 +3474,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>255</v>
       </c>
@@ -3488,7 +3491,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>257</v>
       </c>
@@ -3505,7 +3508,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>259</v>
       </c>
@@ -3522,7 +3525,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>261</v>
       </c>
@@ -3539,7 +3542,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>263</v>
       </c>
@@ -3556,7 +3559,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>265</v>
       </c>
@@ -3573,7 +3576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -3590,7 +3593,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>269</v>
       </c>
@@ -3607,7 +3610,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>271</v>
       </c>
@@ -3624,7 +3627,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>273</v>
       </c>
@@ -3641,7 +3644,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -3658,7 +3661,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>277</v>
       </c>
@@ -3675,7 +3678,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>282</v>
       </c>
@@ -3692,7 +3695,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>281</v>
       </c>
@@ -3709,7 +3712,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>286</v>
       </c>
@@ -3726,7 +3729,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>284</v>
       </c>
@@ -3743,7 +3746,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>287</v>
       </c>
@@ -3835,23 +3838,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AADF751550A837458F675DC0EDA2E01A" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e0f2efc615ea7c2165c722a97587b1e6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ec621e79-30a5-40a0-82cf-20feb35471e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05d8eab6b1e18d03b34a363908ce1f25" ns3:_="">
     <xsd:import namespace="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
@@ -4007,10 +3993,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1CBC5CF-145F-4167-AEBF-D16B799D0B3B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0866F8D-58BC-48E9-A8D4-A37927FA95F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4032,19 +4045,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0866F8D-58BC-48E9-A8D4-A37927FA95F4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1CBC5CF-145F-4167-AEBF-D16B799D0B3B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>